--- a/data/trans_orig/IP07A14-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A14-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse feliz en casa en 2007 (tasa de respuesta: 99,5%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa, percibida por el adulto en 2007 (tasa de respuesta: 99,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>71168</t>
+          <t>71958</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>88729</t>
+          <t>89675</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>74659</t>
+          <t>73933</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>93020</t>
+          <t>93182</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>149893</t>
+          <t>151101</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>176267</t>
+          <t>176722</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,84%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33172</t>
+          <t>31618</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49665</t>
+          <t>49013</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43379</t>
+          <t>42825</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61844</t>
+          <t>62100</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>80675</t>
+          <t>81204</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>106714</t>
+          <t>105794</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,42%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10288</t>
+          <t>9562</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2403</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10259</t>
+          <t>10330</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>6391</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16596</t>
+          <t>17039</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3093</t>
+          <t>3506</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>96626</t>
+          <t>97081</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>119394</t>
+          <t>119645</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>121730</t>
+          <t>121463</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>142816</t>
+          <t>143467</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>224276</t>
+          <t>224518</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>255151</t>
+          <t>255114</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>64,2%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67690</t>
+          <t>67453</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90083</t>
+          <t>89753</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54981</t>
+          <t>54198</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>75378</t>
+          <t>75704</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>129318</t>
+          <t>129171</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>158331</t>
+          <t>158542</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,9%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2698</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11281</t>
+          <t>11403</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12551</t>
+          <t>12367</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8511</t>
+          <t>8572</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19764</t>
+          <t>20271</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>3954</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>173881</t>
+          <t>174321</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>202363</t>
+          <t>202776</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>200880</t>
+          <t>200621</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>229271</t>
+          <t>229733</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>382105</t>
+          <t>383336</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>422273</t>
+          <t>424445</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,75%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>104517</t>
+          <t>105433</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>133432</t>
+          <t>133922</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>104025</t>
+          <t>103871</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>131365</t>
+          <t>132051</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>217383</t>
+          <t>216791</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>257534</t>
+          <t>258134</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,77%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6654</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18643</t>
+          <t>18268</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7646</t>
+          <t>8009</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19634</t>
+          <t>19234</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17706</t>
+          <t>17449</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>32249</t>
+          <t>32646</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3195</t>
+          <t>4154</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2813,7 +2813,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse feliz en casa en 2012 (tasa de respuesta: 97,81%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa, percibida por el adulto en 2012 (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91488</t>
+          <t>92160</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>111727</t>
+          <t>110783</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>92020</t>
+          <t>92324</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>111657</t>
+          <t>110944</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>188970</t>
+          <t>188199</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>217690</t>
+          <t>216647</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,72%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42211</t>
+          <t>42336</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62672</t>
+          <t>61260</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37988</t>
+          <t>38100</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57193</t>
+          <t>56327</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>84784</t>
+          <t>84681</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112149</t>
+          <t>113111</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,4%</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4189</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3540</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12284</t>
+          <t>12098</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4308</t>
+          <t>4209</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14184</t>
+          <t>13302</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3799</t>
+          <t>2746</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>84371</t>
+          <t>83161</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>104578</t>
+          <t>104545</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>105587</t>
+          <t>105530</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>126075</t>
+          <t>125213</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>195203</t>
+          <t>194792</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>225571</t>
+          <t>223056</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>65,3%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55130</t>
+          <t>56048</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75161</t>
+          <t>76480</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42246</t>
+          <t>43373</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61701</t>
+          <t>62369</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>103718</t>
+          <t>104636</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>132733</t>
+          <t>134817</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>39,47%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11225</t>
+          <t>11519</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3931,49 +3931,49 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>6,95%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>6072</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>3022</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>11899</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
           <t>6,77%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>6072</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>3085</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>11269</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>6,41%</t>
-        </is>
-      </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>17</t>
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7392</t>
+          <t>7791</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19420</t>
+          <t>20183</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -4069,7 +4069,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4466</t>
+          <t>4373</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>182340</t>
+          <t>180646</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>210974</t>
+          <t>210346</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>204120</t>
+          <t>203541</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>231921</t>
+          <t>229957</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>392738</t>
+          <t>394004</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>432944</t>
+          <t>434928</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,67%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>102400</t>
+          <t>102923</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>130750</t>
+          <t>131685</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>85080</t>
+          <t>88574</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>112838</t>
+          <t>113729</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>197831</t>
+          <t>195150</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>237598</t>
+          <t>236079</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,19%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>3709</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13115</t>
+          <t>12874</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8006</t>
+          <t>7877</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19400</t>
+          <t>19324</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13394</t>
+          <t>13973</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>28033</t>
+          <t>29077</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4643</t>
+          <t>4169</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>3374</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse feliz en casa en 2016 (tasa de respuesta: 98,72%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa, percibida por el adulto en 2016 (tasa de respuesta: 98,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>120350</t>
+          <t>118912</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>140843</t>
+          <t>140493</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>124353</t>
+          <t>124548</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>144320</t>
+          <t>144490</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>251217</t>
+          <t>251504</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>279201</t>
+          <t>280179</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,35%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39274</t>
+          <t>40164</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58971</t>
+          <t>60230</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37504</t>
+          <t>36406</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57495</t>
+          <t>56232</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>82597</t>
+          <t>82245</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>109678</t>
+          <t>109973</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2920</t>
+          <t>2696</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10791</t>
+          <t>10642</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9529</t>
+          <t>9773</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6148</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16803</t>
+          <t>16601</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>85953</t>
+          <t>85404</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>107423</t>
+          <t>107493</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>94852</t>
+          <t>94690</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>116985</t>
+          <t>116748</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>187625</t>
+          <t>187247</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>216294</t>
+          <t>217056</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>63,08%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53171</t>
+          <t>53936</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74409</t>
+          <t>75273</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51075</t>
+          <t>51678</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72958</t>
+          <t>73655</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>112831</t>
+          <t>112219</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>140340</t>
+          <t>141028</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,98%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>4876</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14134</t>
+          <t>14299</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2271</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10983</t>
+          <t>10942</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9138</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>21323</t>
+          <t>21641</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>4795</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5023</t>
+          <t>4934</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>212762</t>
+          <t>212785</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>242260</t>
+          <t>241958</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>225622</t>
+          <t>226462</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>253489</t>
+          <t>254945</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>445240</t>
+          <t>443888</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>488932</t>
+          <t>485465</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>67,81%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>101117</t>
+          <t>99988</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>130493</t>
+          <t>128408</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>95367</t>
+          <t>94434</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>122534</t>
+          <t>121460</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>201472</t>
+          <t>204383</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>242365</t>
+          <t>243942</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8857</t>
+          <t>9293</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20773</t>
+          <t>21931</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6889,82 +6889,82 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>6,15%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>10760</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>6362</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>16910</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>4,71%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>25157</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>17768</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>34209</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>3,51%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
           <t>2,48%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>5,82%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>10760</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>6278</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>16957</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>25157</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>18560</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>35355</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -7105,7 +7105,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07A14-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A14-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse feliz en casa, percibida por el adulto en 2007 (tasa de respuesta: 99,5%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa, percibida por el/la adulto/a [KIDSCREEN 20] en 2007 (tasa de respuesta: 99,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>83608</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>74994</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>92561</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>59,08%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>52,99%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>65,41%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>80220</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>71958</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>89675</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>71833</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>88095</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>63,22%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>56,71%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>70,67%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>83608</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>73933</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>93182</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>59,08%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>151101</t>
+          <t>150683</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>176722</t>
+          <t>177215</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>66,02%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>52526</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>43931</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>60804</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>37,12%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>31,04%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>42,97%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>40868</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>31618</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>49013</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>33263</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>49564</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>32,21%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>24,92%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>38,62%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>52526</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>42825</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>62100</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>37,12%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>81204</t>
+          <t>80418</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105794</t>
+          <t>105540</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,32%</t>
         </is>
       </c>
     </row>
@@ -953,67 +953,67 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>5381</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2422</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10350</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>7,31%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>5110</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9562</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>9370</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>4,03%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,54%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5381</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2641</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>10330</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>3,8%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6391</t>
+          <t>6333</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17039</t>
+          <t>17415</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -1061,107 +1061,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>696</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3506</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3944</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,55%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3,11%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3899</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>696</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3491</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>126894</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>126894</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>126894</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>131705</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>120659</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>141462</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>64,54%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>59,13%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>69,32%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>107851</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>97081</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>119645</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>96420</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>118928</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>55,79%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>50,22%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>61,89%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>131705</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>121463</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>143467</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>64,54%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>224518</t>
+          <t>223641</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>255114</t>
+          <t>255172</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>64,21%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>65194</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>56033</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>76149</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>31,95%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>27,46%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>37,31%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>78493</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>67453</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>89753</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>67827</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>89559</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>40,61%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>34,89%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>46,43%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>65194</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>54198</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>75704</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>31,95%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>129171</t>
+          <t>127148</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>158542</t>
+          <t>158620</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,92%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7173</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3871</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>12607</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>6,18%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>6298</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2698</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>11403</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>3266</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>11768</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>3,26%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,9%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>7173</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>3840</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>12367</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8572</t>
+          <t>8718</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20271</t>
+          <t>20524</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -1856,74 +1856,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3325</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3320</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>1,72%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3954</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>204072</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>204072</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>204072</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>285</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>193304</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>193304</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>193304</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>204072</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>204072</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>204072</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>215313</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>200700</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>228387</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>62,3%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>58,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>66,09%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>278</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>188071</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>174321</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>202776</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>173879</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>203056</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>58,74%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>54,44%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>63,33%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>215313</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>200621</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>229733</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>62,3%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>383336</t>
+          <t>382305</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>424445</t>
+          <t>423354</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,59%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>117720</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>104437</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>131303</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>34,06%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>30,22%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>37,99%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>119361</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>105433</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>133922</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>105201</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>132781</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>37,28%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>32,93%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>41,82%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>117720</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>103871</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>132051</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>34,06%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>216791</t>
+          <t>216659</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>258134</t>
+          <t>256071</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,46%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>12554</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>8028</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>19918</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,63%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5,76%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>11409</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>6780</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>18268</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>6923</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>17763</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>3,56%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>5,71%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>12554</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>8009</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>19234</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,63%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17449</t>
+          <t>17154</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>32646</t>
+          <t>33777</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -2425,107 +2425,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>696</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4154</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3970</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,22%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3501</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>696</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>3961</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -2538,107 +2538,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3305</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3312</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>1,03%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>4335</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>661</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>3317</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>475</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>320198</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>320198</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>320198</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2813,13 +2813,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse feliz en casa, percibida por el adulto en 2012 (tasa de respuesta: 97,81%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa, percibida por el/la adulto/a [KIDSCREEN 20] en 2012 (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2830,7 +2830,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2998,72 +2998,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>101585</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>91307</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>110484</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>65,44%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>58,82%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>71,17%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>102253</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>92160</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>110783</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>91641</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>111560</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>65,75%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>59,26%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>71,24%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>101585</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>92324</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>110944</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>65,44%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>188199</t>
+          <t>190373</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>216647</t>
+          <t>217336</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,94%</t>
         </is>
       </c>
     </row>
@@ -3111,72 +3111,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>46775</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>38271</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>57945</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>30,13%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>24,65%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>37,33%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>51365</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>42336</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>61260</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>42359</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>61491</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>33,03%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>27,22%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>39,39%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>46775</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>38100</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>56327</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>30,13%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>84681</t>
+          <t>85538</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>113111</t>
+          <t>112208</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,11%</t>
         </is>
       </c>
     </row>
@@ -3224,72 +3224,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6870</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3363</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12167</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>7,84%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>1221</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4244</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3832</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>0,79%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>6870</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>3317</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>12098</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4209</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13302</t>
+          <t>13923</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -3450,107 +3450,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>675</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2767</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3617</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,43%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3342</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>2746</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -3563,57 +3563,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>155230</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>155230</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>155230</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>155514</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>155514</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>155514</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>155230</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>155230</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>155230</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3680,72 +3680,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>115796</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>105201</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>125287</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>65,86%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>59,83%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>71,25%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>94330</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>83161</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>104545</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>83712</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>104244</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>56,91%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>50,17%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>63,08%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>115796</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>105530</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>125213</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>65,86%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>194792</t>
+          <t>196362</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>223056</t>
+          <t>225037</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>65,88%</t>
         </is>
       </c>
     </row>
@@ -3793,72 +3793,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>52695</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>43796</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>63063</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>29,97%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>24,91%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>35,86%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>65271</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>56048</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>76480</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>55409</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>75621</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>39,38%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>33,82%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>46,14%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>52695</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>43373</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>62369</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>29,97%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>104636</t>
+          <t>104294</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>134817</t>
+          <t>132764</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>38,87%</t>
         </is>
       </c>
     </row>
@@ -3906,72 +3906,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6072</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2939</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>11828</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>6,73%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>6143</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2806</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>11519</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2578</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>12793</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>3,71%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,95%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>6072</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>3022</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>11899</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7791</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20183</t>
+          <t>19176</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -4019,107 +4019,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4574</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1271</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4329</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1271</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4373</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -4245,57 +4245,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>175834</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>175834</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>175834</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>165744</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>165744</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>165744</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>175834</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>175834</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>175834</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4362,72 +4362,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>217381</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>203373</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>230489</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>65,66%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>61,43%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>69,62%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>278</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>196583</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>180646</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>210346</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>182568</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>210898</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>61,19%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>56,23%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>65,48%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>217381</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>203541</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>229957</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>65,66%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>394004</t>
+          <t>393286</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>434928</t>
+          <t>433692</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,48%</t>
         </is>
       </c>
     </row>
@@ -4475,72 +4475,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>99470</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>87098</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>113992</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>30,05%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>26,31%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>34,43%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>116635</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>102923</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>131685</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>102445</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>131166</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>36,31%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>32,04%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>40,99%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>99470</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>88574</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>113729</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>30,05%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>195150</t>
+          <t>196485</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>236079</t>
+          <t>237100</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,35%</t>
         </is>
       </c>
     </row>
@@ -4588,72 +4588,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>12942</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>8292</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>19300</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,91%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5,83%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>7365</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>3709</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>12874</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>3544</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>12614</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>2,29%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>4,01%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>12942</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>7877</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>19324</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13973</t>
+          <t>13629</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>29077</t>
+          <t>28475</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -4701,107 +4701,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5285</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>1271</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>4572</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4396</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1271</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4169</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -4814,72 +4814,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>675</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4398</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3385</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4927,57 +4927,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>331064</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>331064</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>331064</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>456</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>321258</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>321258</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>321258</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>482</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>331064</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>331064</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>331064</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5089,13 +5089,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse feliz en casa, percibida por el adulto en 2016 (tasa de respuesta: 98,72%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa, percibida por el/la adulto/a [KIDSCREEN 20] en 2016 (tasa de respuesta: 98,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5106,7 +5106,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5274,72 +5274,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>134443</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>123628</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>144026</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>72,34%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>66,52%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>77,5%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>130677</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>118912</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>140493</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>120233</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>140657</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>70,26%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>63,94%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>75,54%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>134443</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>124548</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>144490</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>72,34%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>251504</t>
+          <t>250266</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>280179</t>
+          <t>278661</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>74,94%</t>
         </is>
       </c>
     </row>
@@ -5387,72 +5387,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>46441</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>37168</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>56565</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>24,99%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>30,44%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>49461</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>40164</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>60230</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>40028</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>59772</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>26,59%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>21,6%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>32,38%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>46441</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>36406</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>56232</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>24,99%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>82245</t>
+          <t>82413</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>109973</t>
+          <t>110411</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,69%</t>
         </is>
       </c>
     </row>
@@ -5500,72 +5500,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4957</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9499</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>5,11%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>5845</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2696</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10642</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2693</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>10593</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>3,14%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>1,45%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,72%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>4957</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2095</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>9773</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6355</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16601</t>
+          <t>17062</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -5839,57 +5839,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>185841</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>185841</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>185841</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>267</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>185983</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>185983</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>185983</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>185841</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>185841</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>185841</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5956,72 +5956,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>105989</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>94854</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>116764</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>61,15%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>54,72%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>67,37%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>96626</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>85404</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>107493</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>86194</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>107922</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>56,58%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>50,01%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>62,94%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>105989</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>94690</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>116748</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>61,15%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>187247</t>
+          <t>187609</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>217056</t>
+          <t>218244</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>63,42%</t>
         </is>
       </c>
     </row>
@@ -6069,72 +6069,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>61537</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>51236</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>72745</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>35,5%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>29,56%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>41,97%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>64619</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>53936</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>75273</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>53634</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>76209</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>37,84%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>31,58%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>44,07%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>61537</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>51678</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>73655</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>35,5%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>112219</t>
+          <t>111252</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141028</t>
+          <t>140776</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,91%</t>
         </is>
       </c>
     </row>
@@ -6182,72 +6182,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5804</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10860</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>6,27%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>8552</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4876</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>14299</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>4814</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>13772</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>5,01%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,37%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>5804</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>2434</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>10942</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9377</t>
+          <t>9008</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>21641</t>
+          <t>21491</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -6408,107 +6408,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>993</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4795</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4921</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,58%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>4941</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>993</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>4934</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -6521,57 +6521,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173330</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>173330</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>173330</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>170789</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>170789</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>170789</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>173330</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>173330</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>173330</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6638,72 +6638,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>240433</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>226207</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>255986</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>66,94%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>62,98%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>71,27%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>327</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>227303</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>212785</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>241958</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>213326</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>242897</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>63,71%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>59,64%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>67,82%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>240433</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>226462</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>254945</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>66,94%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>443888</t>
+          <t>444948</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>485465</t>
+          <t>489104</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>68,32%</t>
         </is>
       </c>
     </row>
@@ -6751,72 +6751,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>107979</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>92389</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>121937</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>30,06%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>25,72%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>33,95%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>114080</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>99988</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>128408</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>98940</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>128045</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>31,98%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>28,03%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>35,99%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>107979</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>94434</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>121460</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>30,06%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>204383</t>
+          <t>202200</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>243942</t>
+          <t>244798</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,19%</t>
         </is>
       </c>
     </row>
@@ -6864,72 +6864,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>10760</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>6173</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>17013</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>14397</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>9293</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>21931</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>9271</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>21747</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>4,04%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>2,6%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>10760</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>6362</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>16910</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17768</t>
+          <t>18356</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>34209</t>
+          <t>33602</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -7090,107 +7090,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>993</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4629</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4972</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>4959</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>993</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>4617</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -7203,57 +7203,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>359172</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>359172</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>359172</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>510</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>356772</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>356772</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>356772</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>493</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>359172</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>359172</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>359172</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
